--- a/data/trans_orig/P36B06_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>766787</t>
+          <t>762408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>820509</t>
+          <t>816463</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1071270</t>
+          <t>1069887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1123048</t>
+          <t>1121385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1847085</t>
+          <t>1846571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1928163</t>
+          <t>1921854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>210172</t>
+          <t>214218</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263894</t>
+          <t>268273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191089</t>
+          <t>192752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242867</t>
+          <t>244250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>416655</t>
+          <t>422964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>497733</t>
+          <t>498247</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1241326</t>
+          <t>1243452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1312937</t>
+          <t>1315902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1226853</t>
+          <t>1225449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1292641</t>
+          <t>1290960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2495291</t>
+          <t>2492480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2587104</t>
+          <t>2586046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,89%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>378646</t>
+          <t>375681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>450257</t>
+          <t>448131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>293972</t>
+          <t>295653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359760</t>
+          <t>361164</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691092</t>
+          <t>692150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>782905</t>
+          <t>785716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>403198</t>
+          <t>404700</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>443979</t>
+          <t>444681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>380287</t>
+          <t>380759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>413494</t>
+          <t>412766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>795912</t>
+          <t>798246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>847445</t>
+          <t>848366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107429</t>
+          <t>106727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148210</t>
+          <t>146708</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62918</t>
+          <t>63646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96125</t>
+          <t>95653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180375</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231908</t>
+          <t>229574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2449382</t>
+          <t>2451498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2544630</t>
+          <t>2550722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2709677</t>
+          <t>2713392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2799375</t>
+          <t>2798214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5177785</t>
+          <t>5185270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5322608</t>
+          <t>5322071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>729041</t>
+          <t>722949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>824289</t>
+          <t>822173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>577787</t>
+          <t>578948</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>667485</t>
+          <t>663770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1328225</t>
+          <t>1328762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1473048</t>
+          <t>1465563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>824953</t>
+          <t>823867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>867263</t>
+          <t>865523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1189661</t>
+          <t>1189882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1234238</t>
+          <t>1234341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2027034</t>
+          <t>2028945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2086090</t>
+          <t>2086447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104317</t>
+          <t>106057</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146627</t>
+          <t>147713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102461</t>
+          <t>102358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147038</t>
+          <t>146817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222189</t>
+          <t>221832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281245</t>
+          <t>279334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1564744</t>
+          <t>1566560</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1630990</t>
+          <t>1634359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1445900</t>
+          <t>1450868</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1510321</t>
+          <t>1513944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3036522</t>
+          <t>3037106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3136404</t>
+          <t>3133172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332009</t>
+          <t>328640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398255</t>
+          <t>396439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>241242</t>
+          <t>237619</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305663</t>
+          <t>300695</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>578158</t>
+          <t>581390</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>678040</t>
+          <t>677456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>379960</t>
+          <t>382629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>415600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>399154</t>
+          <t>401195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>427792</t>
+          <t>427427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>791189</t>
+          <t>789682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>834423</t>
+          <t>835562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64285</t>
+          <t>64541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>97512</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>31204</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59477</t>
+          <t>57436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104349</t>
+          <t>103210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147583</t>
+          <t>149090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2804762</t>
+          <t>2798546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2890113</t>
+          <t>2891720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3070173</t>
+          <t>3068039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3150858</t>
+          <t>3151164</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5898595</t>
+          <t>5897233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6022353</t>
+          <t>6017569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>524607</t>
+          <t>523000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609958</t>
+          <t>616174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>396035</t>
+          <t>395729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>476720</t>
+          <t>478854</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>939260</t>
+          <t>944044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1063018</t>
+          <t>1064380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>622941</t>
+          <t>623933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>660518</t>
+          <t>662007</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>858843</t>
+          <t>857040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>899953</t>
+          <t>899418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1496181</t>
+          <t>1494896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1550722</t>
+          <t>1550059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89839</t>
+          <t>88350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127416</t>
+          <t>126424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93628</t>
+          <t>94163</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134738</t>
+          <t>136541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193216</t>
+          <t>193879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247757</t>
+          <t>249042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1566956</t>
+          <t>1564044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1643036</t>
+          <t>1642352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1568691</t>
+          <t>1567276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1638992</t>
+          <t>1642927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3156666</t>
+          <t>3153349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3261407</t>
+          <t>3258145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430539</t>
+          <t>431223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506619</t>
+          <t>509531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344557</t>
+          <t>340622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>414858</t>
+          <t>416273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>795717</t>
+          <t>798979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>900458</t>
+          <t>903775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>432454</t>
+          <t>428961</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>468207</t>
+          <t>467597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>434634</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>471180</t>
+          <t>469785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>879144</t>
+          <t>878369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>928309</t>
+          <t>929610</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78679</t>
+          <t>79289</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114432</t>
+          <t>117925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77960</t>
+          <t>79355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114506</t>
+          <t>116652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167718</t>
+          <t>166417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216883</t>
+          <t>217658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2643871</t>
+          <t>2646854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2742288</t>
+          <t>2744672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2892536</t>
+          <t>2893217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2983706</t>
+          <t>2979782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5562503</t>
+          <t>5568186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5696296</t>
+          <t>5697827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>628530</t>
+          <t>626146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>726947</t>
+          <t>723964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>542565</t>
+          <t>546489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633735</t>
+          <t>633054</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1200793</t>
+          <t>1199262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1334586</t>
+          <t>1328903</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B06_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>762408</t>
+          <t>765786</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>816463</t>
+          <t>819228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1069887</t>
+          <t>1067803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1121385</t>
+          <t>1121782</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1846571</t>
+          <t>1845504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1921854</t>
+          <t>1925590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214218</t>
+          <t>211453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268273</t>
+          <t>264895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192752</t>
+          <t>192355</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244250</t>
+          <t>246334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>422964</t>
+          <t>419228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>498247</t>
+          <t>499314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1243452</t>
+          <t>1244382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1315902</t>
+          <t>1315340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1225449</t>
+          <t>1228979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1290960</t>
+          <t>1291892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2492480</t>
+          <t>2488209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2586046</t>
+          <t>2589871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375681</t>
+          <t>376243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448131</t>
+          <t>447201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295653</t>
+          <t>294721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361164</t>
+          <t>357634</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692150</t>
+          <t>688325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>785716</t>
+          <t>789987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>404700</t>
+          <t>402369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>444681</t>
+          <t>445146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>380759</t>
+          <t>382013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>412766</t>
+          <t>414221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>798246</t>
+          <t>797676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>848366</t>
+          <t>851487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106727</t>
+          <t>106262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146708</t>
+          <t>149039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63646</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95653</t>
+          <t>94399</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>179454</t>
+          <t>176333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>229574</t>
+          <t>230144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2451498</t>
+          <t>2446669</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2550722</t>
+          <t>2543041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2713392</t>
+          <t>2712791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2798214</t>
+          <t>2798060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5185270</t>
+          <t>5188156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5322071</t>
+          <t>5314879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>722949</t>
+          <t>730630</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>822173</t>
+          <t>827002</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>578948</t>
+          <t>579102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>663770</t>
+          <t>664371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1328762</t>
+          <t>1335954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1465563</t>
+          <t>1462677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>823867</t>
+          <t>828406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>865523</t>
+          <t>866860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1189882</t>
+          <t>1188547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1234341</t>
+          <t>1234400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2028945</t>
+          <t>2031360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2086447</t>
+          <t>2090379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106057</t>
+          <t>104720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147713</t>
+          <t>143174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102358</t>
+          <t>102299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146817</t>
+          <t>148152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221832</t>
+          <t>217900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279334</t>
+          <t>276919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1566560</t>
+          <t>1564626</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1634359</t>
+          <t>1635562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1450868</t>
+          <t>1450365</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1513944</t>
+          <t>1512785</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3037106</t>
+          <t>3038425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3133172</t>
+          <t>3133809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328640</t>
+          <t>327437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>396439</t>
+          <t>398373</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237619</t>
+          <t>238778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300695</t>
+          <t>301198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>581390</t>
+          <t>580753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>677456</t>
+          <t>676137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>382629</t>
+          <t>380173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>415600</t>
+          <t>414982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>401195</t>
+          <t>399641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>427427</t>
+          <t>428091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>789682</t>
+          <t>790038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>835562</t>
+          <t>834827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64541</t>
+          <t>65159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97512</t>
+          <t>99968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31204</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57436</t>
+          <t>58990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103210</t>
+          <t>103945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149090</t>
+          <t>148734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2798546</t>
+          <t>2804839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2891720</t>
+          <t>2895186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3068039</t>
+          <t>3068822</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3151164</t>
+          <t>3148300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5897233</t>
+          <t>5896888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6017569</t>
+          <t>6019294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>523000</t>
+          <t>519534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>616174</t>
+          <t>609881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>395729</t>
+          <t>398593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>478854</t>
+          <t>478071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>944044</t>
+          <t>942319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1064380</t>
+          <t>1064725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>623933</t>
+          <t>622573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>662007</t>
+          <t>660742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>857040</t>
+          <t>858218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>899418</t>
+          <t>901901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1494896</t>
+          <t>1495452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1550059</t>
+          <t>1552563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88350</t>
+          <t>89615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126424</t>
+          <t>127784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94163</t>
+          <t>91680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136541</t>
+          <t>135363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193879</t>
+          <t>191375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249042</t>
+          <t>248486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1564044</t>
+          <t>1568250</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1642352</t>
+          <t>1644189</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1567276</t>
+          <t>1568344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1642927</t>
+          <t>1640712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3153349</t>
+          <t>3156267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3258145</t>
+          <t>3260810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>431223</t>
+          <t>429386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>509531</t>
+          <t>505325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340622</t>
+          <t>342837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>416273</t>
+          <t>415205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>798979</t>
+          <t>796314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>903775</t>
+          <t>900857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>428961</t>
+          <t>430776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>467597</t>
+          <t>468416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>432488</t>
+          <t>434434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>469785</t>
+          <t>470191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>878369</t>
+          <t>876002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>929610</t>
+          <t>927528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79289</t>
+          <t>78470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117925</t>
+          <t>116110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79355</t>
+          <t>78949</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116652</t>
+          <t>114706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166417</t>
+          <t>168499</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>217658</t>
+          <t>220025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2646854</t>
+          <t>2649635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2744672</t>
+          <t>2744884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2893217</t>
+          <t>2897606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2979782</t>
+          <t>2983276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5568186</t>
+          <t>5572723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5697827</t>
+          <t>5696250</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,59%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626146</t>
+          <t>625934</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>723964</t>
+          <t>721183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>546489</t>
+          <t>542995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633054</t>
+          <t>628665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1199262</t>
+          <t>1200839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1328903</t>
+          <t>1324366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
